--- a/IT14_IT15 mapping.xlsx
+++ b/IT14_IT15 mapping.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bankofcanada-my.sharepoint.com/personal/elgh_bank-banque-canada_ca/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bankofcanada-my.sharepoint.com/personal/gong_bank-banque-canada_ca/Documents/MyDocs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60C17CDB-A619-47BE-AE3D-E19CED1A1235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{60C17CDB-A619-47BE-AE3D-E19CED1A1235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A466E7-3335-4A56-9E56-514D977F3FA0}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9B9705B7-FFFE-46C5-9DEE-6D895CFFF971}"/>
+    <workbookView xWindow="25800" yWindow="-6285" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9B9705B7-FFFE-46C5-9DEE-6D895CFFF971}"/>
   </bookViews>
   <sheets>
     <sheet name="BIB Mapping " sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <t>S/4HANA (IT0015 Target Field)</t>
   </si>
@@ -72,6 +73,174 @@
   </si>
   <si>
     <t>ENDDA</t>
+  </si>
+  <si>
+    <t>PA0169</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>EC Field</t>
+  </si>
+  <si>
+    <t>PREAS</t>
+  </si>
+  <si>
+    <t>LONG_SRVC_BNFT</t>
+  </si>
+  <si>
+    <t>PA9000</t>
+  </si>
+  <si>
+    <t>ZZ7N</t>
+  </si>
+  <si>
+    <t>ZZ7S</t>
+  </si>
+  <si>
+    <t>ZZ03</t>
+  </si>
+  <si>
+    <t>ZZ7P</t>
+  </si>
+  <si>
+    <t>ZZ7Q</t>
+  </si>
+  <si>
+    <t>BAREA</t>
+  </si>
+  <si>
+    <t>PLTYP</t>
+  </si>
+  <si>
+    <t>BPLAN</t>
+  </si>
+  <si>
+    <t>BENGR</t>
+  </si>
+  <si>
+    <t>BSTAT</t>
+  </si>
+  <si>
+    <t>ELIDT</t>
+  </si>
+  <si>
+    <t>ENRTY</t>
+  </si>
+  <si>
+    <t>PERIO</t>
+  </si>
+  <si>
+    <t>EEAMT</t>
+  </si>
+  <si>
+    <t>EEPCT</t>
+  </si>
+  <si>
+    <t>EEUNT</t>
+  </si>
+  <si>
+    <t>PTAMT</t>
+  </si>
+  <si>
+    <t>PTPCT</t>
+  </si>
+  <si>
+    <t>PTUNT</t>
+  </si>
+  <si>
+    <t>ELDTO</t>
+  </si>
+  <si>
+    <t>PARDT</t>
+  </si>
+  <si>
+    <t>Field-technical</t>
+  </si>
+  <si>
+    <t>Field name</t>
+  </si>
+  <si>
+    <t>Benefit area</t>
+  </si>
+  <si>
+    <t>Plan type</t>
+  </si>
+  <si>
+    <t>Benefit plan</t>
+  </si>
+  <si>
+    <t>1st Program Grouping</t>
+  </si>
+  <si>
+    <t>2nd Program Grouping</t>
+  </si>
+  <si>
+    <t>Eligible on</t>
+  </si>
+  <si>
+    <t>Elig. override</t>
+  </si>
+  <si>
+    <t>Particip.date</t>
+  </si>
+  <si>
+    <t>Type of enrol.</t>
+  </si>
+  <si>
+    <t>EVENT</t>
+  </si>
+  <si>
+    <t>Adjust. reason</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Pre-Tax Amount</t>
+  </si>
+  <si>
+    <t>Pre-Tax Units</t>
+  </si>
+  <si>
+    <t>Pre-Tax Percent</t>
+  </si>
+  <si>
+    <t>Post-Tax Amount</t>
+  </si>
+  <si>
+    <t>Post-Tax Percent</t>
+  </si>
+  <si>
+    <t>Post-Tax Units</t>
+  </si>
+  <si>
+    <t>Change Reason</t>
+  </si>
+  <si>
+    <t>Long Service Benefit</t>
+  </si>
+  <si>
+    <t>Downsizing</t>
+  </si>
+  <si>
+    <t>7N Tech Pen Serv Dat</t>
+  </si>
+  <si>
+    <t>DOWNSIZING_FLAG</t>
+  </si>
+  <si>
+    <t>7S Pens Plan Code Ef</t>
+  </si>
+  <si>
+    <t>03 Pens fund re-entr</t>
+  </si>
+  <si>
+    <t>7P 1.5% Add Flex Ben</t>
+  </si>
+  <si>
+    <t>7Q 35 yrs Credited S</t>
   </si>
 </sst>
 </file>
@@ -597,28 +766,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87DBBBAE-1540-48C8-83FD-2B24F4305A6D}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="14" max="14" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N4" t="s">
         <v>3</v>
       </c>
@@ -626,12 +795,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N6" t="s">
         <v>4</v>
       </c>
@@ -639,7 +808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -661,32 +830,32 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N18" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N20" t="s">
         <v>3</v>
       </c>
@@ -701,4 +870,242 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3825758C-8FEC-4FE5-8787-549903A21BD8}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/IT14_IT15 mapping.xlsx
+++ b/IT14_IT15 mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bankofcanada-my.sharepoint.com/personal/gong_bank-banque-canada_ca/Documents/MyDocs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/irisibm/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{60C17CDB-A619-47BE-AE3D-E19CED1A1235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A466E7-3335-4A56-9E56-514D977F3FA0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0815B5DF-557C-4F46-9C52-DFC00AA08B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="-6285" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9B9705B7-FFFE-46C5-9DEE-6D895CFFF971}"/>
+    <workbookView xWindow="30240" yWindow="3220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9B9705B7-FFFE-46C5-9DEE-6D895CFFF971}"/>
   </bookViews>
   <sheets>
     <sheet name="BIB Mapping " sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="95">
   <si>
     <t>S/4HANA (IT0015 Target Field)</t>
   </si>
@@ -241,6 +241,90 @@
   </si>
   <si>
     <t>7Q 35 yrs Credited S</t>
+  </si>
+  <si>
+    <t>Labels</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>cust_longServiceBenefit</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>cust_TechPenServDate</t>
+  </si>
+  <si>
+    <t>7N Tech Pen Serv Date</t>
+  </si>
+  <si>
+    <t>cust_PensPlanCodeEff</t>
+  </si>
+  <si>
+    <t>7S Pens Plan Code Eff</t>
+  </si>
+  <si>
+    <t>cust_PensFundReEntry</t>
+  </si>
+  <si>
+    <t>03 Pens Fund Re Entry</t>
+  </si>
+  <si>
+    <t>cust_AddFlexBen</t>
+  </si>
+  <si>
+    <t>cust_yearsOfService35</t>
+  </si>
+  <si>
+    <t>35 Years of Service</t>
+  </si>
+  <si>
+    <t>cust_benefitArea</t>
+  </si>
+  <si>
+    <t>Benefit Area</t>
+  </si>
+  <si>
+    <t>cust_planType</t>
+  </si>
+  <si>
+    <t>Plan Type</t>
+  </si>
+  <si>
+    <t>cust_plan</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>cust_eligibleOn</t>
+  </si>
+  <si>
+    <t>Eligible On</t>
+  </si>
+  <si>
+    <t>cust_eligOverride</t>
+  </si>
+  <si>
+    <t>Elig. Override</t>
+  </si>
+  <si>
+    <t>cust_participationDate</t>
+  </si>
+  <si>
+    <t>Participation Date</t>
+  </si>
+  <si>
+    <t>cust_enrollmentType</t>
+  </si>
+  <si>
+    <t>Enrollment Type</t>
+  </si>
+  <si>
+    <t>cust_period</t>
   </si>
 </sst>
 </file>
@@ -264,7 +348,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,8 +361,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -286,14 +382,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,28 +880,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87DBBBAE-1540-48C8-83FD-2B24F4305A6D}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="14" max="14" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N4" t="s">
         <v>3</v>
       </c>
@@ -795,12 +909,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N6" t="s">
         <v>4</v>
       </c>
@@ -808,7 +922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -830,32 +944,32 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N18" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="14:15" x14ac:dyDescent="0.2">
       <c r="N20" t="s">
         <v>3</v>
       </c>
@@ -874,236 +988,408 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3825758C-8FEC-4FE5-8787-549903A21BD8}">
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="C18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="C23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="C24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="C26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="5" t="s">
         <v>57</v>
       </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
